--- a/2026/ROSALES/Febrero/expensas rosales Febrero.xlsx
+++ b/2026/ROSALES/Febrero/expensas rosales Febrero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ROSALES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264F9F2B-E3FC-4F75-A1B5-B294E452BA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E658E4-DCA7-4FA4-980F-73EDD43082E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,16 +18,16 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="123">
   <si>
     <t>TOTAL</t>
   </si>
@@ -323,13 +323,7 @@
     <t>Seguro de vida Sra encargada</t>
   </si>
   <si>
-    <t>Christian / Vanina</t>
-  </si>
-  <si>
     <t>CAJA ANTERIOR</t>
-  </si>
-  <si>
-    <t>Brian</t>
   </si>
   <si>
     <t>Gastos extraordinarios:</t>
@@ -354,9 +348,6 @@
 Les recordamos que el pago debe realizarse con dinero justo.</t>
   </si>
   <si>
-    <t>LAS LINEAS GRISES CORRESPONDEN A PLANES DE PAGO VIGENTES -  RESTA ABONAR 6 CUOTAS DE $107.386,20 + LAS EXPENSAS AL DIA - PARTE DE LA DEUDA CANCELA EDESUR Y EXPENSAS CON TASA DE INTERES MENSUAL</t>
-  </si>
-  <si>
     <t>Fumigacion</t>
   </si>
   <si>
@@ -378,18 +369,6 @@
     <t xml:space="preserve">Subidos en EN3R0 </t>
   </si>
   <si>
-    <t>TSG MES 12</t>
-  </si>
-  <si>
-    <t>Servisur - cambio de plafones en sala de medidores</t>
-  </si>
-  <si>
-    <t>Casa ruan - Compra de materiales electricos</t>
-  </si>
-  <si>
-    <t>CUOTA PLAN DE PAGOS (6/6)</t>
-  </si>
-  <si>
     <t>PREVISION EXTRAORDINARIA - ARBA</t>
   </si>
   <si>
@@ -403,6 +382,21 @@
   </si>
   <si>
     <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Carnevalli Christian</t>
+  </si>
+  <si>
+    <t>Espacio Edesur</t>
+  </si>
+  <si>
+    <t>Ascensores Lema - Puesta en marcha de ascensor - Trabajos realizados con mecanismos de puerta en 2do piso</t>
+  </si>
+  <si>
+    <t>ARBA - Cuota 3 del plan</t>
+  </si>
+  <si>
+    <t>No llego factura</t>
   </si>
 </sst>
 </file>
@@ -663,7 +657,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -721,12 +715,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1034,7 +1022,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1245,18 +1233,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -1269,8 +1245,6 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1298,35 +1272,6 @@
     <xf numFmtId="174" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="26" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="25" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="26" fillId="11" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1336,7 +1281,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1352,7 +1297,6 @@
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1362,9 +1306,6 @@
     <xf numFmtId="171" fontId="34" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1374,10 +1315,8 @@
     <xf numFmtId="171" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1392,9 +1331,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1413,11 +1349,34 @@
     <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="26" fillId="6" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1835,7 +1794,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F67"/>
+  <dimension ref="A2:F63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1873,10 +1832,10 @@
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1925,10 +1884,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="238">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
@@ -1939,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="239">
+      <c r="C19" s="213">
         <v>358727.59</v>
       </c>
       <c r="D19" s="20"/>
@@ -1950,29 +1909,29 @@
         <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="238">
+      <c r="C20" s="33">
         <v>85000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="240" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="238">
+    <row r="21" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="204" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="205"/>
+      <c r="C21" s="33">
         <v>130000</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B22" s="39"/>
-      <c r="C22" s="238">
+      <c r="C22" s="33">
         <v>1034026.5</v>
       </c>
       <c r="D22" s="20"/>
@@ -1980,366 +1939,325 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>22</v>
+      </c>
       <c r="C23" s="33">
-        <v>21996</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="6"/>
+        <v>89200</v>
+      </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="33">
-        <v>89200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="23">
-        <f>SUM(C17:C24)</f>
-        <v>1795604.09</v>
-      </c>
+      <c r="A24" s="40"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="23">
+        <f>SUM(C17:C23)</f>
+        <v>1773608.09</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="178"/>
+      <c r="D25" s="45"/>
+      <c r="F25" s="12"/>
     </row>
     <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="208"/>
+      <c r="A26" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="33">
+        <f>349151.87+ (349151.87*10%)</f>
+        <v>384067.05699999997</v>
+      </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="42"/>
+        <v>97</v>
+      </c>
+      <c r="B27" s="28"/>
       <c r="C27" s="33">
-        <f>349151.87+ (349151.87*10%)</f>
-        <v>384067.05699999997</v>
+        <v>7458</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="238">
-        <v>7458</v>
+        <v>117</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="33">
+        <v>84450</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="28" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B29" s="42"/>
-      <c r="C29" s="33">
-        <v>54000</v>
-      </c>
-      <c r="D29" s="45"/>
+      <c r="C29" s="206" t="s">
+        <v>122</v>
+      </c>
       <c r="F29" s="12"/>
     </row>
     <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="33">
-        <v>18000</v>
-      </c>
-      <c r="D30" s="45"/>
+        <v>91</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="238">
-        <v>84450</v>
-      </c>
-      <c r="D31" s="45"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="23">
+        <f>SUM(C25:C30)</f>
+        <v>475975.05699999997</v>
+      </c>
       <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="43">
+        <f>+C31+C24</f>
+        <v>2249583.1469999999</v>
+      </c>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C33" s="24"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="24"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="173"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="173"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="34"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C38" s="25"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="157" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="157"/>
+      <c r="C39" s="158">
+        <v>500000</v>
+      </c>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C40" s="25"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14">
+        <f>+C35+C36+C37+C40</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19">
+        <f>+C41+C32</f>
+        <v>2249583.1469999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="163" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="164">
+        <v>-141024.51037612878</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="163" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="177">
+        <f>-(C43-C30)</f>
+        <v>-2249583.1469999999</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="163" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="165">
+        <f>'prorrateo '!F31</f>
+        <v>4417369.1316235811</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="163" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="176">
+        <v>-987480.77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="163" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="33">
-        <v>55000</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="40"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="23">
-        <f>SUM(C26:C33)</f>
-        <v>602975.05700000003</v>
-      </c>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="43">
-        <f>+C34+C25</f>
-        <v>2398579.1469999999</v>
-      </c>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C36" s="24"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="24"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="202"/>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="202"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="34"/>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C41" s="25"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="167" t="s">
-        <v>120</v>
-      </c>
-      <c r="B42" s="167"/>
-      <c r="C42" s="168">
-        <v>1500000</v>
-      </c>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C43" s="25"/>
-      <c r="F43" s="12"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14">
-        <f>+C38+C39+C40+C43</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19">
-        <f>+C44+C35</f>
-        <v>2398579.1469999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="C48" s="149"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="192" t="s">
-        <v>99</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="193">
-        <v>39116.323591710112</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="192" t="s">
-        <v>123</v>
-      </c>
       <c r="B50" s="28"/>
-      <c r="C50" s="207">
-        <f>-(C46-C33)</f>
-        <v>-2398579.1469999999</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
+      <c r="C50" s="31">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="192" t="s">
-        <v>95</v>
+      <c r="A51" s="163" t="s">
+        <v>8</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="194">
-        <f>'prorrateo '!F31</f>
-        <v>2899814.6830321611</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="192" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="206">
-        <v>-987480.77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="192" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="192" t="s">
-        <v>119</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="215">
-        <v>107386.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="192" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="193">
-        <f>SUM(C49:C54)</f>
-        <v>-339742.71037612873</v>
-      </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="10"/>
+      <c r="C51" s="164">
+        <f>SUM(C46:C50)</f>
+        <v>1039280.7042474523</v>
+      </c>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="10"/>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="190"/>
+      <c r="B53" s="190"/>
+      <c r="C53" s="190"/>
+      <c r="F53" s="44"/>
+    </row>
+    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="191"/>
+      <c r="B54" s="191"/>
+      <c r="C54" s="191"/>
+    </row>
+    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="27"/>
+      <c r="C55" s="29"/>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="31">
+        <f>-C41</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="225"/>
-      <c r="B57" s="225"/>
-      <c r="C57" s="225"/>
-      <c r="F57" s="44"/>
-    </row>
-    <row r="58" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="226"/>
-      <c r="B58" s="226"/>
-      <c r="C58" s="226"/>
-    </row>
-    <row r="59" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="29"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="31">
-        <f>-C44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="31"/>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="32"/>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="150" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="151"/>
-      <c r="C63" s="152">
-        <f>SUM(C59:C62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="227" t="s">
-        <v>107</v>
-      </c>
-      <c r="B64" s="228"/>
-      <c r="C64" s="228"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="228"/>
-      <c r="B65" s="228"/>
-      <c r="C65" s="228"/>
-    </row>
-    <row r="66" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="228"/>
-      <c r="B66" s="228"/>
-      <c r="C66" s="228"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="31"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="32"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="143"/>
+      <c r="C59" s="144">
+        <f>SUM(C55:C58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" s="193"/>
+      <c r="C60" s="193"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="193"/>
+      <c r="B61" s="193"/>
+      <c r="C61" s="193"/>
+    </row>
+    <row r="62" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="193"/>
+      <c r="B62" s="193"/>
+      <c r="C62" s="193"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A57:C58"/>
-    <mergeCell ref="A64:C66"/>
+  <mergeCells count="3">
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="A60:C62"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2357,7 +2275,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
@@ -2365,7 +2283,7 @@
     <col min="3" max="3" width="13.88671875" customWidth="1"/>
     <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.109375" customWidth="1"/>
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
     <col min="9" max="10" width="10.6640625" customWidth="1"/>
@@ -2379,32 +2297,34 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="229">
+        <v>100</v>
+      </c>
+      <c r="B1" s="194">
         <f>N1</f>
-        <v>2168873.477</v>
-      </c>
-      <c r="C1" s="229"/>
+        <v>2249583.1469999999</v>
+      </c>
+      <c r="C1" s="194"/>
       <c r="D1" s="135">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="232" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="229">
-        <v>1500000</v>
-      </c>
-      <c r="M1" s="229"/>
+        <v>99</v>
+      </c>
+      <c r="G1" s="195">
+        <v>0</v>
+      </c>
+      <c r="H1" s="195"/>
+      <c r="I1" s="196" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="194">
+        <v>500000</v>
+      </c>
+      <c r="M1" s="194"/>
       <c r="N1">
-        <v>2168873.477</v>
+        <v>2249583.1469999999</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2429,26 +2349,26 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="191" t="s">
+      <c r="H2" s="162" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L2" s="50" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M2" s="51" t="s">
         <v>30</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -2465,13 +2385,13 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="126">
-        <v>153001.36328172</v>
-      </c>
-      <c r="F3" s="204">
-        <f>E3</f>
-        <v>153001.36328172</v>
-      </c>
-      <c r="G3" s="211">
+        <v>245146.06472309006</v>
+      </c>
+      <c r="F3" s="175">
+        <f t="shared" ref="F3" si="0">E3</f>
+        <v>245146.06472309006</v>
+      </c>
+      <c r="G3" s="181">
         <f>E3-F3</f>
         <v>0</v>
       </c>
@@ -2481,11 +2401,11 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>110829.43467469999</v>
+        <v>114953.69881170001</v>
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
-        <v>56083.170331390029</v>
+        <v>56073.660329590006</v>
       </c>
       <c r="K3" s="56">
         <f>G$1*D3/100</f>
@@ -2493,25 +2413,23 @@
       </c>
       <c r="L3" s="56">
         <f>L$1*D3/100</f>
-        <v>76650.000000000015</v>
+        <v>25550</v>
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>243562.60500609005</v>
+        <v>196577.35914129001</v>
       </c>
       <c r="N3" s="44"/>
-      <c r="O3" s="146">
+      <c r="O3" s="138">
         <f>M3-J3</f>
-        <v>187479.43467470002</v>
+        <v>140503.69881170001</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="59" t="s">
-        <v>100</v>
-      </c>
+      <c r="B4" s="59"/>
       <c r="C4" s="60" t="s">
         <v>34</v>
       </c>
@@ -2519,44 +2437,43 @@
         <v>5.09</v>
       </c>
       <c r="E4" s="126">
-        <v>148167.69116867997</v>
-      </c>
-      <c r="F4" s="204">
-        <f>E4</f>
-        <v>148167.69116867997</v>
-      </c>
-      <c r="G4" s="211">
-        <f t="shared" ref="G4:G29" si="0">E4-F4</f>
-        <v>0</v>
+        <v>237726.73859071001</v>
+      </c>
+      <c r="F4" s="175">
+        <v>110474</v>
+      </c>
+      <c r="G4" s="181">
+        <f t="shared" ref="G4:G29" si="1">E4-F4</f>
+        <v>127252.73859071001</v>
       </c>
       <c r="H4" s="56">
-        <f t="shared" ref="H4:H29" si="1">IF(G4&gt;0,G4*4%,0)</f>
-        <v>0</v>
+        <f t="shared" ref="H4:H29" si="2">IF(G4&gt;0,G4*4%,0)</f>
+        <v>5090.1095436284004</v>
       </c>
       <c r="I4" s="56">
-        <f t="shared" ref="I4:I29" si="2">B$1*D4/100</f>
-        <v>110395.65997929999</v>
+        <f t="shared" ref="I4:I29" si="3">B$1*D4/100</f>
+        <v>114503.7821823</v>
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
-        <v>49403.816388410014</v>
+        <v>32949.206114210021</v>
       </c>
       <c r="K4" s="56">
-        <f t="shared" ref="K4:K29" si="3">G$1*D4/100</f>
+        <f t="shared" ref="K4:K29" si="4">G$1*D4/100</f>
         <v>0</v>
       </c>
       <c r="L4" s="56">
-        <f t="shared" ref="L4:L29" si="4">L$1*D4/100</f>
-        <v>76350</v>
+        <f t="shared" ref="L4:L29" si="5">L$1*D4/100</f>
+        <v>25450</v>
       </c>
       <c r="M4" s="57">
-        <f t="shared" ref="M4:M29" si="5">I4+G4+L4+K4+H4+J4</f>
-        <v>236149.47636771001</v>
+        <f t="shared" ref="M4:M29" si="6">I4+G4+L4+K4+H4+J4</f>
+        <v>305245.8364308484</v>
       </c>
       <c r="N4" s="44"/>
-      <c r="O4" s="146">
-        <f t="shared" ref="O4:O29" si="6">M4-J4</f>
-        <v>186745.65997929999</v>
+      <c r="O4" s="138">
+        <f t="shared" ref="O4:O29" si="7">M4-J4</f>
+        <v>272296.63031663839</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -2571,94 +2488,97 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="126">
-        <v>187753.45675376873</v>
-      </c>
-      <c r="F5" s="204">
-        <f>215804.85-F23</f>
-        <v>187753.46389584002</v>
-      </c>
-      <c r="G5" s="211">
-        <f t="shared" si="0"/>
-        <v>-7.1420712920371443E-3</v>
+        <v>254798.71871768872</v>
+      </c>
+      <c r="F5" s="175">
+        <f>301940.37-F23</f>
+        <v>254798.71925147998</v>
+      </c>
+      <c r="G5" s="181">
+        <f t="shared" si="1"/>
+        <v>-5.3379125893115997E-4</v>
       </c>
       <c r="H5" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I5" s="56">
-        <f t="shared" si="2"/>
-        <v>109311.2232408</v>
+        <f t="shared" si="3"/>
+        <v>113378.9906088</v>
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
-        <v>68325.734130960016</v>
+        <v>65764.448675759995</v>
       </c>
       <c r="K5" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L5" s="56">
-        <f t="shared" si="4"/>
-        <v>75600</v>
+        <f t="shared" si="5"/>
+        <v>25200</v>
       </c>
       <c r="M5" s="57">
-        <f t="shared" si="5"/>
-        <v>253236.95022968872</v>
+        <f t="shared" si="6"/>
+        <v>204343.43875076872</v>
       </c>
       <c r="N5" s="44"/>
-      <c r="O5" s="146">
-        <f t="shared" si="6"/>
-        <v>184911.21609872871</v>
+      <c r="O5" s="138">
+        <f t="shared" si="7"/>
+        <v>138578.99007500871</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="190"/>
+      <c r="B6" s="161"/>
       <c r="C6" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="170">
+      <c r="D6" s="160">
         <v>5.21</v>
       </c>
       <c r="E6" s="126">
-        <v>151256.37574692001</v>
-      </c>
-      <c r="F6" s="204"/>
-      <c r="G6" s="212">
-        <f t="shared" si="0"/>
-        <v>151256.37574692001</v>
+        <v>390207.9854617868</v>
+      </c>
+      <c r="F6" s="175">
+        <f>E6</f>
+        <v>390207.9854617868</v>
+      </c>
+      <c r="G6" s="182">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H6" s="64">
-        <f t="shared" si="1"/>
-        <v>6050.2550298768001</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I6" s="64">
-        <f t="shared" si="2"/>
-        <v>112998.3081517</v>
+        <f t="shared" si="3"/>
+        <v>117203.28195869998</v>
       </c>
       <c r="J6" s="64">
         <f>Edesur!N13</f>
-        <v>40138.599346289993</v>
+        <v>44952.17960648999</v>
       </c>
       <c r="K6" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L6" s="64">
-        <f t="shared" si="4"/>
-        <v>78150</v>
-      </c>
-      <c r="M6" s="203">
         <f t="shared" si="5"/>
-        <v>388593.53827478678</v>
-      </c>
-      <c r="O6" s="146">
+        <v>26050</v>
+      </c>
+      <c r="M6" s="174">
         <f t="shared" si="6"/>
-        <v>348454.93892849679</v>
-      </c>
-      <c r="P6" s="169"/>
+        <v>188205.46156518997</v>
+      </c>
+      <c r="O6" s="138">
+        <f t="shared" si="7"/>
+        <v>143253.28195869998</v>
+      </c>
+      <c r="P6" s="159"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
@@ -2674,45 +2594,45 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="126">
-        <v>152954.46978172002</v>
-      </c>
-      <c r="F7" s="204">
-        <f>181005.86-F28</f>
-        <v>152954.47389584</v>
-      </c>
-      <c r="G7" s="211">
-        <f t="shared" si="0"/>
-        <v>-4.1141199762932956E-3</v>
+        <v>244958.48660897004</v>
+      </c>
+      <c r="F7" s="175">
+        <f>199250.14+92850-F28</f>
+        <v>244958.48925148</v>
+      </c>
+      <c r="G7" s="181">
+        <f t="shared" si="1"/>
+        <v>-2.642509964061901E-3</v>
       </c>
       <c r="H7" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="56">
-        <f t="shared" si="2"/>
-        <v>110829.43467469999</v>
+        <f t="shared" si="3"/>
+        <v>114953.69881170001</v>
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
-        <v>55895.596331389985</v>
+        <v>58709.075029589992</v>
       </c>
       <c r="K7" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L7" s="56">
-        <f t="shared" si="4"/>
-        <v>76650.000000000015</v>
+        <f t="shared" si="5"/>
+        <v>25550</v>
       </c>
       <c r="M7" s="57">
-        <f t="shared" si="5"/>
-        <v>243375.02689197002</v>
-      </c>
-      <c r="O7" s="146">
         <f t="shared" si="6"/>
-        <v>187479.43056058005</v>
-      </c>
-      <c r="P7" s="169"/>
+        <v>199212.77119878004</v>
+      </c>
+      <c r="O7" s="138">
+        <f t="shared" si="7"/>
+        <v>140503.69616919005</v>
+      </c>
+      <c r="P7" s="159"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
@@ -2726,43 +2646,43 @@
         <v>5.09</v>
       </c>
       <c r="E8" s="126">
-        <v>153579.20106868001</v>
-      </c>
-      <c r="F8" s="204">
-        <f t="shared" ref="F8:F10" si="7">E8</f>
-        <v>153579.20106868001</v>
-      </c>
-      <c r="G8" s="211">
-        <f t="shared" si="0"/>
+        <v>244451.26649070997</v>
+      </c>
+      <c r="F8" s="175">
+        <f t="shared" ref="F8:F10" si="8">E8</f>
+        <v>244451.26649070997</v>
+      </c>
+      <c r="G8" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="56">
-        <f t="shared" si="2"/>
-        <v>110395.65997929999</v>
+        <f t="shared" si="3"/>
+        <v>114503.7821823</v>
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
-        <v>56128.344288409993</v>
+        <v>62295.158414209989</v>
       </c>
       <c r="K8" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L8" s="56">
-        <f t="shared" si="4"/>
-        <v>76350</v>
+        <f t="shared" si="5"/>
+        <v>25450</v>
       </c>
       <c r="M8" s="57">
-        <f t="shared" si="5"/>
-        <v>242874.00426770997</v>
-      </c>
-      <c r="O8" s="146">
         <f t="shared" si="6"/>
-        <v>186745.65997929999</v>
+        <v>202248.94059650999</v>
+      </c>
+      <c r="O8" s="138">
+        <f t="shared" si="7"/>
+        <v>139953.7821823</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -2777,94 +2697,92 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="126">
-        <v>145197.56902720104</v>
-      </c>
-      <c r="F9" s="204">
+        <v>231697.00892309</v>
+      </c>
+      <c r="F9" s="175">
         <f>E9</f>
-        <v>145197.56902720104</v>
-      </c>
-      <c r="G9" s="211">
-        <f t="shared" si="0"/>
+        <v>231697.00892309</v>
+      </c>
+      <c r="G9" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="56">
-        <f t="shared" si="2"/>
-        <v>110829.43467469999</v>
+        <f t="shared" si="3"/>
+        <v>114953.69881170001</v>
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
-        <v>42634.114531389976</v>
+        <v>45513.244129590013</v>
       </c>
       <c r="K9" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="56">
+        <f t="shared" si="5"/>
+        <v>25550</v>
+      </c>
+      <c r="M9" s="57">
+        <f t="shared" si="6"/>
+        <v>186016.94294129004</v>
+      </c>
+      <c r="O9" s="138">
+        <f t="shared" si="7"/>
+        <v>140503.69881170001</v>
+      </c>
+      <c r="P9" s="159"/>
+    </row>
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="202" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="203"/>
+      <c r="C10" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="160">
+        <v>5.09</v>
+      </c>
+      <c r="E10" s="126">
+        <v>224924.81309071</v>
+      </c>
+      <c r="F10" s="175">
+        <f>379452.66-F22</f>
+        <v>332311.00925147999</v>
+      </c>
+      <c r="G10" s="182">
+        <f t="shared" si="1"/>
+        <v>-107386.19616076999</v>
+      </c>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="56">
+        <v>114503.7821823</v>
+      </c>
+      <c r="J10" s="64">
+        <f>Edesur!N17</f>
+        <v>36438.08251421</v>
+      </c>
+      <c r="K10" s="64">
         <f t="shared" si="4"/>
-        <v>76650.000000000015</v>
-      </c>
-      <c r="M9" s="57">
+        <v>0</v>
+      </c>
+      <c r="L10" s="64">
         <f t="shared" si="5"/>
-        <v>230113.54920608999</v>
-      </c>
-      <c r="O9" s="146">
+        <v>25450</v>
+      </c>
+      <c r="M10" s="174">
         <f t="shared" si="6"/>
-        <v>187479.43467470002</v>
-      </c>
-      <c r="P9" s="169"/>
-    </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="171" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="172" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="173" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="174">
-        <v>5.09</v>
-      </c>
-      <c r="E10" s="175">
-        <v>135028.13246867998</v>
-      </c>
-      <c r="F10" s="224">
+        <v>69005.668535739998</v>
+      </c>
+      <c r="O10" s="138">
         <f t="shared" si="7"/>
-        <v>135028.13246867998</v>
-      </c>
-      <c r="G10" s="213">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176">
-        <f t="shared" si="2"/>
-        <v>110395.65997929999</v>
-      </c>
-      <c r="J10" s="176">
-        <f>Edesur!N17</f>
-        <v>36601.890888410009</v>
-      </c>
-      <c r="K10" s="176">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="176">
-        <f t="shared" si="4"/>
-        <v>76350</v>
-      </c>
-      <c r="M10" s="177">
-        <f t="shared" si="5"/>
-        <v>223347.55086771</v>
-      </c>
-      <c r="O10" s="146">
-        <f t="shared" si="6"/>
-        <v>186745.65997929999</v>
+        <v>32567.586021529998</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -2879,40 +2797,43 @@
         <v>5.04</v>
       </c>
       <c r="E11" s="126">
-        <v>143136.29328608001</v>
-      </c>
-      <c r="F11" s="204"/>
-      <c r="G11" s="211">
-        <f t="shared" si="0"/>
-        <v>143136.29328608001</v>
+        <v>379810.43677728315</v>
+      </c>
+      <c r="F11" s="175">
+        <f>E11</f>
+        <v>379810.43677728315</v>
+      </c>
+      <c r="G11" s="181">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H11" s="56">
-        <f t="shared" si="1"/>
-        <v>5725.4517314432005</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I11" s="56">
-        <f t="shared" si="2"/>
-        <v>109311.2232408</v>
+        <f t="shared" si="3"/>
+        <v>113378.9906088</v>
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
-        <v>44475.700030960012</v>
+        <v>43527.550975760001</v>
       </c>
       <c r="K11" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L11" s="56">
-        <f t="shared" si="4"/>
-        <v>75600</v>
+        <f t="shared" si="5"/>
+        <v>25200</v>
       </c>
       <c r="M11" s="57">
-        <f t="shared" si="5"/>
-        <v>378248.66828928317</v>
-      </c>
-      <c r="O11" s="146">
         <f t="shared" si="6"/>
-        <v>333772.96825832315</v>
+        <v>182106.54158456001</v>
+      </c>
+      <c r="O11" s="138">
+        <f t="shared" si="7"/>
+        <v>138578.9906088</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -2927,43 +2848,43 @@
         <v>5.21</v>
       </c>
       <c r="E12" s="126">
-        <v>167106.37874692006</v>
-      </c>
-      <c r="F12" s="204">
-        <f t="shared" ref="F12" si="8">E12</f>
-        <v>167106.37874692006</v>
-      </c>
-      <c r="G12" s="211">
-        <f t="shared" si="0"/>
+        <v>253412.57158498999</v>
+      </c>
+      <c r="F12" s="175">
+        <f t="shared" ref="F12" si="9">E12</f>
+        <v>253412.57158498999</v>
+      </c>
+      <c r="G12" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H12" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="56">
-        <f t="shared" si="2"/>
-        <v>112998.3081517</v>
+        <f t="shared" si="3"/>
+        <v>117203.28195869998</v>
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
-        <v>60649.816246289978</v>
+        <v>68736.562806489994</v>
       </c>
       <c r="K12" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L12" s="56">
-        <f t="shared" si="4"/>
-        <v>78150</v>
+        <f t="shared" si="5"/>
+        <v>26050</v>
       </c>
       <c r="M12" s="57">
-        <f t="shared" si="5"/>
-        <v>251798.12439799</v>
-      </c>
-      <c r="O12" s="146">
         <f t="shared" si="6"/>
-        <v>191148.30815170001</v>
+        <v>211989.84476518998</v>
+      </c>
+      <c r="O12" s="138">
+        <f t="shared" si="7"/>
+        <v>143253.28195869998</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -2980,97 +2901,97 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="126">
-        <v>162201.86798172005</v>
-      </c>
-      <c r="F13" s="204">
-        <f>190253.26-F24</f>
-        <v>162201.87389584002</v>
-      </c>
-      <c r="G13" s="211">
-        <f t="shared" si="0"/>
-        <v>-5.9141199744772166E-3</v>
+        <v>253624.40360897002</v>
+      </c>
+      <c r="F13" s="175">
+        <f>300766.05-F24</f>
+        <v>253624.39925147998</v>
+      </c>
+      <c r="G13" s="181">
+        <f t="shared" si="1"/>
+        <v>4.3574900482781231E-3</v>
       </c>
       <c r="H13" s="56">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1.7429960193112492E-4</v>
       </c>
       <c r="I13" s="56">
-        <f t="shared" si="2"/>
-        <v>110829.43467469999</v>
+        <f t="shared" si="3"/>
+        <v>114953.69881170001</v>
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
-        <v>64561.515131389999</v>
+        <v>64608.277329590012</v>
       </c>
       <c r="K13" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L13" s="56">
-        <f t="shared" si="4"/>
-        <v>76650.000000000015</v>
+        <f t="shared" si="5"/>
+        <v>25550</v>
       </c>
       <c r="M13" s="57">
-        <f t="shared" si="5"/>
-        <v>252040.94389197003</v>
+        <f t="shared" si="6"/>
+        <v>205111.98067307967</v>
       </c>
       <c r="N13" s="44"/>
-      <c r="O13" s="146">
-        <f t="shared" si="6"/>
-        <v>187479.42876058002</v>
+      <c r="O13" s="138">
+        <f t="shared" si="7"/>
+        <v>140503.70334348967</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="190" t="s">
-        <v>105</v>
+      <c r="B14" s="161" t="s">
+        <v>103</v>
       </c>
       <c r="C14" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="170">
+      <c r="D14" s="160">
         <v>5.09</v>
       </c>
       <c r="E14" s="126">
-        <v>138995.71226398699</v>
-      </c>
-      <c r="F14" s="204">
-        <f>167047.02-F25</f>
-        <v>138995.63389584</v>
-      </c>
-      <c r="G14" s="212">
-        <f t="shared" si="0"/>
-        <v>7.8368146991124377E-2</v>
+        <v>228413.77099358285</v>
+      </c>
+      <c r="F14" s="175">
+        <f>275555.42-F25</f>
+        <v>228413.76925147997</v>
+      </c>
+      <c r="G14" s="182">
+        <f t="shared" si="1"/>
+        <v>1.7421028751414269E-3</v>
       </c>
       <c r="H14" s="64">
-        <f t="shared" si="1"/>
-        <v>3.134725879644975E-3</v>
+        <f t="shared" si="2"/>
+        <v>6.9684115005657076E-5</v>
       </c>
       <c r="I14" s="64">
-        <f t="shared" si="2"/>
-        <v>110395.65997929999</v>
+        <f t="shared" si="3"/>
+        <v>114503.7821823</v>
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
-        <v>40090.767288409996</v>
+        <v>40799.178014210003</v>
       </c>
       <c r="K14" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L14" s="56">
-        <f t="shared" si="4"/>
-        <v>76350</v>
+        <f t="shared" si="5"/>
+        <v>25450</v>
       </c>
       <c r="M14" s="57">
-        <f t="shared" si="5"/>
-        <v>226836.50877058285</v>
-      </c>
-      <c r="O14" s="146">
         <f t="shared" si="6"/>
-        <v>186745.74148217286</v>
+        <v>180752.96200829698</v>
+      </c>
+      <c r="O14" s="138">
+        <f t="shared" si="7"/>
+        <v>139953.78399408696</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -3087,43 +3008,40 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="126">
-        <v>279407.3046097632</v>
-      </c>
-      <c r="F15" s="204">
-        <f>334072.62-F29</f>
-        <v>279407.29774156125</v>
-      </c>
-      <c r="G15" s="211">
-        <f t="shared" si="0"/>
-        <v>6.8682019482366741E-3</v>
+        <v>229298.04770269</v>
+      </c>
+      <c r="F15" s="175"/>
+      <c r="G15" s="181">
+        <f t="shared" si="1"/>
+        <v>229298.04770269</v>
       </c>
       <c r="H15" s="56">
-        <f t="shared" si="1"/>
-        <v>2.7472807792946699E-4</v>
+        <f t="shared" si="2"/>
+        <v>9171.9219081076008</v>
       </c>
       <c r="I15" s="56">
-        <f t="shared" si="2"/>
-        <v>109311.2232408</v>
+        <f t="shared" si="3"/>
+        <v>113378.9906088</v>
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
-        <v>42825.048830959975</v>
+        <v>64882.850875760028</v>
       </c>
       <c r="K15" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L15" s="56">
-        <f t="shared" si="4"/>
-        <v>75600</v>
+        <f t="shared" si="5"/>
+        <v>25200</v>
       </c>
       <c r="M15" s="57">
-        <f t="shared" si="5"/>
-        <v>227736.27921469</v>
-      </c>
-      <c r="O15" s="146">
         <f t="shared" si="6"/>
-        <v>184911.23038373003</v>
+        <v>441931.81109535758</v>
+      </c>
+      <c r="O15" s="138">
+        <f t="shared" si="7"/>
+        <v>377048.96021959756</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
@@ -3140,44 +3058,44 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="126">
-        <v>159322.05774691998</v>
-      </c>
-      <c r="F16" s="204">
-        <f>187373.45-F21</f>
-        <v>159322.06389584002</v>
-      </c>
-      <c r="G16" s="211">
-        <f t="shared" si="0"/>
-        <v>-6.1489200452342629E-3</v>
+        <v>257482.92123606999</v>
+      </c>
+      <c r="F16" s="175">
+        <f>304624.57-F21</f>
+        <v>257482.91925147999</v>
+      </c>
+      <c r="G16" s="181">
+        <f t="shared" si="1"/>
+        <v>1.9845899951178581E-3</v>
       </c>
       <c r="H16" s="56">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>7.9383599804714328E-5</v>
       </c>
       <c r="I16" s="56">
-        <f t="shared" si="2"/>
-        <v>112998.3081517</v>
+        <f t="shared" si="3"/>
+        <v>117203.28195869998</v>
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
-        <v>64720.172046290027</v>
+        <v>57585.288506490018</v>
       </c>
       <c r="K16" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L16" s="56">
-        <f t="shared" si="4"/>
-        <v>78150</v>
+        <f t="shared" si="5"/>
+        <v>26050</v>
       </c>
       <c r="M16" s="57">
-        <f t="shared" si="5"/>
-        <v>255868.47404906998</v>
+        <f t="shared" si="6"/>
+        <v>200838.57252916362</v>
       </c>
       <c r="N16" s="44"/>
-      <c r="O16" s="146">
-        <f t="shared" si="6"/>
-        <v>191148.30200277996</v>
+      <c r="O16" s="138">
+        <f t="shared" si="7"/>
+        <v>143253.28402267362</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -3192,196 +3110,192 @@
         <v>5.04</v>
       </c>
       <c r="E17" s="126">
-        <v>135108.12608607998</v>
-      </c>
-      <c r="F17" s="204">
-        <f>E17+134891.87</f>
-        <v>269999.99608607998</v>
-      </c>
-      <c r="G17" s="211">
-        <f t="shared" si="0"/>
-        <v>-134891.87</v>
+        <v>97801.259959760006</v>
+      </c>
+      <c r="F17" s="175"/>
+      <c r="G17" s="181">
+        <f t="shared" si="1"/>
+        <v>97801.259959760006</v>
       </c>
       <c r="H17" s="56">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>3912.0503983904005</v>
       </c>
       <c r="I17" s="56">
-        <f t="shared" si="2"/>
-        <v>109311.2232408</v>
+        <f t="shared" si="3"/>
+        <v>113378.9906088</v>
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
-        <v>46220.138230960001</v>
+        <v>35780.744775759988</v>
       </c>
       <c r="K17" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L17" s="56">
-        <f t="shared" si="4"/>
-        <v>75600</v>
+        <f t="shared" si="5"/>
+        <v>25200</v>
       </c>
       <c r="M17" s="57">
-        <f t="shared" si="5"/>
-        <v>96239.491471760004</v>
-      </c>
-      <c r="O17" s="146">
         <f t="shared" si="6"/>
-        <v>50019.353240800003</v>
+        <v>276073.04574271035</v>
+      </c>
+      <c r="O17" s="138">
+        <f t="shared" si="7"/>
+        <v>240292.30096695037</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="196" t="s">
+      <c r="A18" s="167" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="197"/>
+      <c r="B18" s="168"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="170">
+      <c r="D18" s="160">
         <v>5.21</v>
       </c>
       <c r="E18" s="126">
-        <v>142824.92444691999</v>
-      </c>
-      <c r="F18" s="204">
-        <f t="shared" ref="F18:F21" si="9">E18</f>
-        <v>142824.92444691999</v>
-      </c>
-      <c r="G18" s="212">
-        <f t="shared" si="0"/>
+        <v>239269.49198499002</v>
+      </c>
+      <c r="F18" s="175">
+        <f t="shared" ref="F18:F21" si="10">E18</f>
+        <v>239269.49198499002</v>
+      </c>
+      <c r="G18" s="182">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H18" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I18" s="64">
-        <f t="shared" si="2"/>
-        <v>112998.3081517</v>
+        <f t="shared" si="3"/>
+        <v>117203.28195869998</v>
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
-        <v>46506.736646290003</v>
+        <v>48459.81340649</v>
       </c>
       <c r="K18" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="64">
-        <f t="shared" si="4"/>
-        <v>78150</v>
+        <f t="shared" si="5"/>
+        <v>26050</v>
       </c>
       <c r="M18" s="57">
-        <f t="shared" si="5"/>
-        <v>237655.04479799001</v>
-      </c>
-      <c r="N18" s="199"/>
-      <c r="O18" s="146">
         <f t="shared" si="6"/>
-        <v>191148.30815170001</v>
-      </c>
-      <c r="P18" s="198"/>
-      <c r="Q18" s="195"/>
+        <v>191713.09536518998</v>
+      </c>
+      <c r="N18" s="170"/>
+      <c r="O18" s="138">
+        <f t="shared" si="7"/>
+        <v>143253.28195869998</v>
+      </c>
+      <c r="P18" s="169"/>
+      <c r="Q18" s="166"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="190"/>
+      <c r="B19" s="161"/>
       <c r="C19" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="170">
+      <c r="D19" s="160">
         <v>7.4</v>
       </c>
       <c r="E19" s="126">
-        <v>225198.20842479993</v>
-      </c>
-      <c r="F19" s="204">
-        <f t="shared" si="9"/>
-        <v>225198.20842479993</v>
-      </c>
-      <c r="G19" s="212">
-        <f t="shared" si="0"/>
+        <v>374177.79418060009</v>
+      </c>
+      <c r="F19" s="175">
+        <f t="shared" si="10"/>
+        <v>374177.79418060009</v>
+      </c>
+      <c r="G19" s="182">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I19" s="64">
-        <f t="shared" si="2"/>
-        <v>160496.63729800002</v>
+        <f t="shared" si="3"/>
+        <v>166469.15287799999</v>
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
-        <v>100388.08410260003</v>
+        <v>91349.268190600007</v>
       </c>
       <c r="K19" s="64">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="64">
+        <f t="shared" si="5"/>
+        <v>37000</v>
+      </c>
+      <c r="M19" s="57">
+        <f t="shared" si="6"/>
+        <v>294818.42106860003</v>
+      </c>
+      <c r="O19" s="138">
+        <f t="shared" si="7"/>
+        <v>203469.15287800002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="203"/>
+      <c r="C20" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="160">
+        <v>1.08</v>
+      </c>
+      <c r="E20" s="126">
+        <v>399381.20189270412</v>
+      </c>
+      <c r="F20" s="175">
+        <v>0</v>
+      </c>
+      <c r="G20" s="182">
+        <f t="shared" si="1"/>
+        <v>399381.20189270412</v>
+      </c>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="64">
+        <v>24295.4979876</v>
+      </c>
+      <c r="J20" s="64">
+        <f>Edesur!N27</f>
+        <v>6905.6180305199996</v>
+      </c>
+      <c r="K20" s="64">
         <f t="shared" si="4"/>
-        <v>111000</v>
-      </c>
-      <c r="M19" s="57">
+        <v>0</v>
+      </c>
+      <c r="L20" s="64">
         <f t="shared" si="5"/>
-        <v>371884.72140060004</v>
-      </c>
-      <c r="O19" s="146">
+        <v>5400</v>
+      </c>
+      <c r="M20" s="174">
         <f t="shared" si="6"/>
-        <v>271496.63729800005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
-      <c r="A20" s="178"/>
-      <c r="B20" s="172" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="173" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="174">
-        <v>1.08</v>
-      </c>
-      <c r="E20" s="175">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F20" s="224">
-        <f t="shared" si="9"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G20" s="213">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="176"/>
-      <c r="I20" s="176">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
-      </c>
-      <c r="J20" s="176">
-        <f>Edesur!N27</f>
-        <v>7183.1525209199999</v>
-      </c>
-      <c r="K20" s="176">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="176">
-        <f t="shared" si="4"/>
-        <v>16200</v>
-      </c>
-      <c r="M20" s="177">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O20" s="146">
-        <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>435982.31791082409</v>
+      </c>
+      <c r="O20" s="138">
+        <f t="shared" si="7"/>
+        <v>429076.69988030411</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -3396,91 +3310,93 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F21" s="204">
-        <f t="shared" si="9"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G21" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F21" s="175">
+        <f t="shared" si="10"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G21" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H21" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I21" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K21" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="56">
+        <f t="shared" si="5"/>
+        <v>5400</v>
+      </c>
+      <c r="M21" s="57">
+        <f t="shared" si="6"/>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O21" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="161"/>
+      <c r="C22" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="160">
+        <v>1.08</v>
+      </c>
+      <c r="E22" s="126">
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F22" s="175">
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G22" s="182">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="64">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="56">
+        <v>24295.4979876</v>
+      </c>
+      <c r="J22" s="64">
+        <f>Edesur!N29</f>
+        <v>6905.6180305199996</v>
+      </c>
+      <c r="K22" s="64">
         <f t="shared" si="4"/>
-        <v>16200</v>
-      </c>
-      <c r="M21" s="57">
+        <v>0</v>
+      </c>
+      <c r="L22" s="64">
         <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O21" s="146">
+        <v>5400</v>
+      </c>
+      <c r="M22" s="174">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="136"/>
-      <c r="B22" s="137"/>
-      <c r="C22" s="138" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="139">
-        <v>1.08</v>
-      </c>
-      <c r="E22" s="140">
-        <v>338691.87610017706</v>
-      </c>
-      <c r="F22" s="205">
-        <v>0</v>
-      </c>
-      <c r="G22" s="214">
-        <f t="shared" si="0"/>
-        <v>338691.87610017706</v>
-      </c>
-      <c r="H22" s="141">
-        <f t="shared" si="1"/>
-        <v>13547.675044007083</v>
-      </c>
-      <c r="I22" s="141">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
-      </c>
-      <c r="J22" s="141">
-        <f>Edesur!N29</f>
-        <v>7183.1525209199999</v>
-      </c>
-      <c r="K22" s="141">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="141">
-        <f t="shared" si="4"/>
-        <v>16200</v>
-      </c>
-      <c r="M22" s="142">
-        <f t="shared" si="5"/>
-        <v>399046.53721670411</v>
-      </c>
-      <c r="O22" s="146">
-        <f t="shared" si="6"/>
-        <v>391863.38469578413</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O22" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -3495,43 +3411,43 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F23" s="204">
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F23" s="175">
         <f>E23</f>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G23" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G23" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H23" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I23" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K23" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L23" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M23" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O23" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O23" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -3548,51 +3464,51 @@
         <v>1.08</v>
       </c>
       <c r="E24" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F24" s="204">
-        <f t="shared" ref="F24" si="10">E24</f>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G24" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F24" s="175">
+        <f t="shared" ref="F24" si="11">E24</f>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G24" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H24" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I24" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K24" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L24" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M24" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O24" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O24" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="190" t="s">
-        <v>105</v>
+      <c r="B25" s="161" t="s">
+        <v>103</v>
       </c>
       <c r="C25" s="60" t="s">
         <v>70</v>
@@ -3601,43 +3517,43 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F25" s="204">
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F25" s="175">
         <f>E25</f>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G25" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G25" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H25" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I25" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K25" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L25" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M25" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O25" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O25" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -3652,43 +3568,43 @@
         <v>1.08</v>
       </c>
       <c r="E26" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F26" s="204">
-        <f t="shared" ref="F26:F28" si="11">E26</f>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G26" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F26" s="175">
+        <f t="shared" ref="F26:F28" si="12">E26</f>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G26" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H26" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I26" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K26" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L26" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M26" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O26" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O26" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -3703,47 +3619,47 @@
         <v>1.08</v>
       </c>
       <c r="E27" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F27" s="204">
-        <f t="shared" si="11"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G27" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F27" s="175">
+        <f t="shared" si="12"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G27" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H27" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I27" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K27" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L27" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M27" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O27" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O27" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
-        <v>281300.98063311994</v>
+        <v>468461.09567764011</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -3759,43 +3675,43 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="126">
-        <v>28051.386104159999</v>
-      </c>
-      <c r="F28" s="204">
-        <f t="shared" si="11"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="G28" s="211">
-        <f t="shared" si="0"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F28" s="175">
+        <f t="shared" si="12"/>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="G28" s="181">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H28" s="56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I28" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K28" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L28" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M28" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O28" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>36601.116018119996</v>
+      </c>
+      <c r="O28" s="138">
+        <f t="shared" si="7"/>
+        <v>29695.497987599996</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
@@ -3812,43 +3728,40 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="126">
-        <v>54665.322258438733</v>
-      </c>
-      <c r="F29" s="204">
-        <f>E29</f>
-        <v>54665.322258438733</v>
-      </c>
-      <c r="G29" s="211">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47141.650748520005</v>
+      </c>
+      <c r="F29" s="175"/>
+      <c r="G29" s="181">
+        <f t="shared" si="1"/>
+        <v>47141.650748520005</v>
       </c>
       <c r="H29" s="56">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1885.6660299408002</v>
       </c>
       <c r="I29" s="56">
-        <f t="shared" si="2"/>
-        <v>23423.833551600004</v>
+        <f t="shared" si="3"/>
+        <v>24295.4979876</v>
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="K29" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L29" s="56">
-        <f t="shared" si="4"/>
-        <v>16200</v>
+        <f t="shared" si="5"/>
+        <v>5400</v>
       </c>
       <c r="M29" s="57">
-        <f t="shared" si="5"/>
-        <v>46806.986072520005</v>
-      </c>
-      <c r="O29" s="146">
         <f t="shared" si="6"/>
-        <v>39623.833551600008</v>
+        <v>85628.43279658079</v>
+      </c>
+      <c r="O29" s="138">
+        <f t="shared" si="7"/>
+        <v>78722.814766060794</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -3879,13 +3792,13 @@
       <c r="E31" s="73"/>
       <c r="F31" s="132">
         <f>SUM(F3:F30)</f>
-        <v>2899814.6830321611</v>
+        <v>4417369.1316235811</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
       <c r="I31" s="133">
         <f>SUM(I3:I30)</f>
-        <v>2168873.4770000014</v>
+        <v>2249583.1469999999</v>
       </c>
       <c r="J31" s="133"/>
       <c r="K31" s="133">
@@ -3895,81 +3808,21 @@
       <c r="L31" s="132"/>
       <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>5179870.3692650739</v>
+        <v>4550612.3728449307</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="230" t="s">
-        <v>108</v>
-      </c>
-      <c r="B33" s="230"/>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="230"/>
-      <c r="K33" s="230"/>
-      <c r="L33" s="230"/>
-      <c r="M33" s="230"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="230"/>
-      <c r="B34" s="230"/>
-      <c r="C34" s="230"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="230"/>
-      <c r="F34" s="230"/>
-      <c r="G34" s="230"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="230"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="230"/>
-      <c r="M34" s="230"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="230"/>
-      <c r="B35" s="230"/>
-      <c r="C35" s="230"/>
-      <c r="D35" s="230"/>
-      <c r="E35" s="230"/>
-      <c r="F35" s="230"/>
-      <c r="G35" s="230"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="230"/>
-      <c r="J35" s="230"/>
-      <c r="K35" s="230"/>
-      <c r="L35" s="230"/>
-      <c r="M35" s="230"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="230"/>
-      <c r="B36" s="230"/>
-      <c r="C36" s="230"/>
-      <c r="D36" s="230"/>
-      <c r="E36" s="230"/>
-      <c r="F36" s="230"/>
-      <c r="G36" s="230"/>
-      <c r="H36" s="230"/>
-      <c r="I36" s="230"/>
-      <c r="J36" s="230"/>
-      <c r="K36" s="230"/>
-      <c r="L36" s="230"/>
-      <c r="M36" s="230"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E40" s="21"/>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="F34" s="44"/>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E36" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A33:M36"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:M1"/>
@@ -3990,129 +3843,129 @@
     <col min="3" max="3" width="15.109375" customWidth="1"/>
     <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="0.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="13" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="5.109375" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12.88671875" customWidth="1"/>
     <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
-      <c r="M1" s="234"/>
-      <c r="N1" s="235"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="199"/>
       <c r="O1" s="76"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
-      <c r="L3" s="156"/>
-      <c r="M3" s="156"/>
-      <c r="N3" s="156"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="146"/>
+      <c r="N3" s="146"/>
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="156" t="s">
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="146" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="156"/>
-      <c r="K4" s="156"/>
-      <c r="L4" s="156"/>
-      <c r="M4" s="156"/>
-      <c r="N4" s="156"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="156"/>
-      <c r="J5" s="156"/>
-      <c r="K5" s="156"/>
-      <c r="L5" s="156"/>
-      <c r="M5" s="156"/>
-      <c r="N5" s="156"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="201" t="str">
+      <c r="C6" s="172" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 13/03</v>
       </c>
       <c r="D6" s="28"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
-      <c r="L6" s="156"/>
-      <c r="M6" s="156"/>
-      <c r="N6" s="156"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="147"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
@@ -4121,21 +3974,21 @@
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="210">
-        <f>-'detalle y gastos'!C52</f>
+      <c r="C7" s="180">
+        <f>-'detalle y gastos'!C49</f>
         <v>987480.77</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
-      <c r="L7" s="156"/>
-      <c r="M7" s="156"/>
-      <c r="N7" s="156"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
@@ -4151,15 +4004,15 @@
       <c r="H8" s="83"/>
       <c r="I8" s="82"/>
       <c r="J8" s="78"/>
-      <c r="K8" s="209">
+      <c r="K8" s="179">
         <f>C8-J38</f>
-        <v>-322374.05510000011</v>
-      </c>
-      <c r="L8" s="237">
+        <v>-348071.69310000003</v>
+      </c>
+      <c r="L8" s="201">
         <f>C7-J38</f>
-        <v>665106.7148999999</v>
-      </c>
-      <c r="M8" s="237"/>
+        <v>639409.07689999999</v>
+      </c>
+      <c r="M8" s="201"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
@@ -4195,10 +4048,10 @@
       <c r="J9" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="216" t="s">
+      <c r="K9" s="183" t="s">
         <v>84</v>
       </c>
-      <c r="L9" s="216" t="s">
+      <c r="L9" s="183" t="s">
         <v>84</v>
       </c>
       <c r="M9" s="122" t="s">
@@ -4226,42 +4079,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="102">
-        <v>4657.8999999999996</v>
+        <v>4893.5</v>
       </c>
       <c r="G10" s="102">
-        <v>4893.5</v>
+        <v>5143</v>
       </c>
       <c r="H10" s="103">
         <f>G10-F10</f>
-        <v>235.60000000000036</v>
+        <v>249.5</v>
       </c>
       <c r="I10" s="104">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>16.492000000000026</v>
+        <v>17.465000000000003</v>
       </c>
       <c r="J10" s="114">
         <f>M10*93.787</f>
-        <v>22096.217200000036</v>
+        <v>23399.856500000002</v>
       </c>
       <c r="K10" s="114">
         <f>K8*E10%</f>
-        <v>-16473.314215610008</v>
-      </c>
-      <c r="L10" s="219">
+        <v>-17786.463517410004</v>
+      </c>
+      <c r="L10" s="186">
         <f>L$8*E10/S$12</f>
-        <v>33986.953131389993</v>
+        <v>32673.803829590004</v>
       </c>
       <c r="M10" s="105">
         <f>G10-F10</f>
-        <v>235.60000000000036</v>
+        <v>249.5</v>
       </c>
       <c r="N10" s="103">
         <f>J10+L10</f>
-        <v>56083.170331390029</v>
+        <v>56073.660329590006</v>
       </c>
       <c r="O10" s="96">
         <f>N10+'prorrateo '!M3</f>
-        <v>299645.77533748007</v>
+        <v>252651.01947088001</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -4282,42 +4135,42 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="102">
-        <v>4378</v>
+        <v>4543.8</v>
       </c>
       <c r="G11" s="102">
-        <v>4543.8</v>
+        <v>4548.1000000000004</v>
       </c>
       <c r="H11" s="103">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>165.80000000000018</v>
+        <v>4.3000000000001819</v>
       </c>
       <c r="I11" s="104">
         <f t="shared" si="0"/>
-        <v>11.606000000000014</v>
+        <v>0.30100000000001276</v>
       </c>
       <c r="J11" s="114">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>15549.884600000018</v>
+        <v>403.28410000001708</v>
       </c>
       <c r="K11" s="114">
         <f>K8*E11%</f>
-        <v>-16408.839404590006</v>
-      </c>
-      <c r="L11" s="219">
+        <v>-17716.849178790002</v>
+      </c>
+      <c r="L11" s="186">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>33853.931788409995</v>
+        <v>32545.922014210002</v>
       </c>
       <c r="M11" s="105">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>165.80000000000018</v>
+        <v>4.3000000000001819</v>
       </c>
       <c r="N11" s="103">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>49403.816388410014</v>
+        <v>32949.206114210021</v>
       </c>
       <c r="O11" s="96">
         <f>N11+'prorrateo '!M4</f>
-        <v>285553.29275612003</v>
+        <v>338195.04254505842</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4338,42 +4191,42 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="102">
-        <v>1981.8</v>
+        <v>2352.9</v>
       </c>
       <c r="G12" s="102">
-        <v>2352.9</v>
+        <v>2710.5</v>
       </c>
       <c r="H12" s="103">
         <f t="shared" si="1"/>
-        <v>371.10000000000014</v>
+        <v>357.59999999999991</v>
       </c>
       <c r="I12" s="104">
         <f t="shared" si="0"/>
-        <v>25.977000000000011</v>
+        <v>25.031999999999996</v>
       </c>
       <c r="J12" s="114">
         <f t="shared" si="2"/>
-        <v>34804.355700000015</v>
+        <v>33538.231199999995</v>
       </c>
       <c r="K12" s="114">
         <f>K8*E12%</f>
-        <v>-16247.652377040005</v>
-      </c>
-      <c r="L12" s="219">
+        <v>-17542.813332240003</v>
+      </c>
+      <c r="L12" s="186">
         <f t="shared" si="3"/>
-        <v>33521.378430959994</v>
+        <v>32226.217475760001</v>
       </c>
       <c r="M12" s="105">
         <f>G12-F12</f>
-        <v>371.10000000000014</v>
+        <v>357.59999999999991</v>
       </c>
       <c r="N12" s="103">
         <f t="shared" si="5"/>
-        <v>68325.734130960016</v>
+        <v>65764.448675759995</v>
       </c>
       <c r="O12" s="96">
         <f>N12+'prorrateo '!M5</f>
-        <v>321562.68436064874</v>
+        <v>270107.88742652873</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4387,52 +4240,52 @@
       <c r="B13" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="159" t="s">
+      <c r="C13" s="149" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="160">
+      <c r="E13" s="150">
         <v>5.21</v>
       </c>
       <c r="F13" s="102">
-        <v>1453</v>
+        <v>1511.5</v>
       </c>
       <c r="G13" s="102">
-        <v>1511.5</v>
+        <v>1635.6</v>
       </c>
       <c r="H13" s="103">
         <f t="shared" si="1"/>
-        <v>58.5</v>
-      </c>
-      <c r="I13" s="161">
+        <v>124.09999999999991</v>
+      </c>
+      <c r="I13" s="151">
         <f t="shared" si="0"/>
-        <v>4.0950000000000006</v>
+        <v>8.6869999999999941</v>
       </c>
       <c r="J13" s="114">
         <f t="shared" si="2"/>
-        <v>5486.5395000000008</v>
-      </c>
-      <c r="K13" s="220">
+        <v>11638.966699999992</v>
+      </c>
+      <c r="K13" s="187">
         <f>K8*E13%</f>
-        <v>-16795.688270710005</v>
-      </c>
-      <c r="L13" s="219">
+        <v>-18134.535210510003</v>
+      </c>
+      <c r="L13" s="186">
         <f t="shared" si="3"/>
-        <v>34652.059846289994</v>
-      </c>
-      <c r="M13" s="162">
+        <v>33313.21290649</v>
+      </c>
+      <c r="M13" s="152">
         <f t="shared" si="4"/>
-        <v>58.5</v>
+        <v>124.09999999999991</v>
       </c>
       <c r="N13" s="103">
         <f t="shared" si="5"/>
-        <v>40138.599346289993</v>
+        <v>44952.17960648999</v>
       </c>
       <c r="O13" s="96">
         <f>N13+'prorrateo '!M6</f>
-        <v>428732.13762107678</v>
+        <v>233157.64117167995</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4453,42 +4306,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="102">
-        <v>2130</v>
+        <v>2363.6</v>
       </c>
       <c r="G14" s="102">
-        <v>2363.6</v>
+        <v>2641.2</v>
       </c>
       <c r="H14" s="103">
         <f t="shared" si="1"/>
-        <v>233.59999999999991</v>
+        <v>277.59999999999991</v>
       </c>
       <c r="I14" s="104">
         <f t="shared" si="0"/>
-        <v>16.351999999999997</v>
+        <v>19.431999999999995</v>
       </c>
       <c r="J14" s="114">
         <f t="shared" si="2"/>
-        <v>21908.643199999991</v>
+        <v>26035.271199999992</v>
       </c>
       <c r="K14" s="114">
         <f>K8*E14%</f>
-        <v>-16473.314215610008</v>
-      </c>
-      <c r="L14" s="219">
+        <v>-17786.463517410004</v>
+      </c>
+      <c r="L14" s="186">
         <f t="shared" si="3"/>
-        <v>33986.953131389993</v>
+        <v>32673.803829590004</v>
       </c>
       <c r="M14" s="105">
         <f t="shared" si="4"/>
-        <v>233.59999999999991</v>
+        <v>277.59999999999991</v>
       </c>
       <c r="N14" s="103">
         <f t="shared" si="5"/>
-        <v>55895.596331389985</v>
+        <v>58709.075029589992</v>
       </c>
       <c r="O14" s="96">
         <f>N14+'prorrateo '!M7</f>
-        <v>299270.62322335999</v>
+        <v>257921.84622837004</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4509,42 +4362,42 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="102">
-        <v>3326.8</v>
+        <v>3564.3</v>
       </c>
       <c r="G15" s="102">
-        <v>3564.3</v>
+        <v>3881.5</v>
       </c>
       <c r="H15" s="103">
         <f t="shared" si="1"/>
-        <v>237.5</v>
+        <v>317.19999999999982</v>
       </c>
       <c r="I15" s="104">
         <f t="shared" si="0"/>
-        <v>16.625</v>
+        <v>22.20399999999999</v>
       </c>
       <c r="J15" s="114">
         <f t="shared" si="2"/>
-        <v>22274.412500000002</v>
+        <v>29749.236399999983</v>
       </c>
       <c r="K15" s="114">
         <f>K8*E15%</f>
-        <v>-16408.839404590006</v>
-      </c>
-      <c r="L15" s="219">
+        <v>-17716.849178790002</v>
+      </c>
+      <c r="L15" s="186">
         <f t="shared" si="3"/>
-        <v>33853.931788409995</v>
+        <v>32545.922014210002</v>
       </c>
       <c r="M15" s="105">
         <f t="shared" si="4"/>
-        <v>237.5</v>
+        <v>317.19999999999982</v>
       </c>
       <c r="N15" s="103">
         <f t="shared" si="5"/>
-        <v>56128.344288409993</v>
+        <v>62295.158414209989</v>
       </c>
       <c r="O15" s="96">
         <f>N15+'prorrateo '!M8</f>
-        <v>299002.34855611995</v>
+        <v>264544.09901071998</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -4564,42 +4417,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="102">
-        <v>2744.5</v>
+        <v>2836.7</v>
       </c>
       <c r="G16" s="102">
-        <v>2836.7</v>
+        <v>2973.6</v>
       </c>
       <c r="H16" s="103">
         <f t="shared" si="1"/>
-        <v>92.199999999999818</v>
+        <v>136.90000000000009</v>
       </c>
       <c r="I16" s="104">
         <f t="shared" si="0"/>
-        <v>6.4539999999999882</v>
+        <v>9.5830000000000073</v>
       </c>
       <c r="J16" s="114">
         <f t="shared" si="2"/>
-        <v>8647.1613999999827</v>
+        <v>12839.440300000009</v>
       </c>
       <c r="K16" s="114">
         <f>K8*E16%</f>
-        <v>-16473.314215610008</v>
-      </c>
-      <c r="L16" s="219">
+        <v>-17786.463517410004</v>
+      </c>
+      <c r="L16" s="186">
         <f t="shared" si="3"/>
-        <v>33986.953131389993</v>
+        <v>32673.803829590004</v>
       </c>
       <c r="M16" s="105">
         <f t="shared" si="4"/>
-        <v>92.199999999999818</v>
+        <v>136.90000000000009</v>
       </c>
       <c r="N16" s="103">
         <f t="shared" si="5"/>
-        <v>42634.114531389976</v>
+        <v>45513.244129590013</v>
       </c>
       <c r="O16" s="96">
         <f>N16+'prorrateo '!M9</f>
-        <v>272747.66373747995</v>
+        <v>231530.18707088006</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -4609,52 +4462,52 @@
       <c r="B17" s="88">
         <v>9</v>
       </c>
-      <c r="C17" s="179" t="s">
+      <c r="C17" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="180" t="s">
+      <c r="D17" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="181">
+      <c r="E17" s="100">
         <v>5.09</v>
       </c>
-      <c r="F17" s="182">
-        <v>3430.2</v>
-      </c>
-      <c r="G17" s="182">
+      <c r="F17" s="102">
         <v>3459.5</v>
       </c>
-      <c r="H17" s="183">
+      <c r="G17" s="102">
+        <v>3501</v>
+      </c>
+      <c r="H17" s="103">
         <f t="shared" si="1"/>
-        <v>29.300000000000182</v>
-      </c>
-      <c r="I17" s="184">
+        <v>41.5</v>
+      </c>
+      <c r="I17" s="104">
         <f t="shared" si="0"/>
-        <v>2.051000000000013</v>
-      </c>
-      <c r="J17" s="185">
+        <v>2.9050000000000002</v>
+      </c>
+      <c r="J17" s="114">
         <f t="shared" si="2"/>
-        <v>2747.9591000000173</v>
-      </c>
-      <c r="K17" s="185">
+        <v>3892.1605000000004</v>
+      </c>
+      <c r="K17" s="114">
         <f>K8*E17%</f>
-        <v>-16408.839404590006</v>
-      </c>
-      <c r="L17" s="221">
+        <v>-17716.849178790002</v>
+      </c>
+      <c r="L17" s="186">
         <f t="shared" si="3"/>
-        <v>33853.931788409995</v>
-      </c>
-      <c r="M17" s="186">
+        <v>32545.922014210002</v>
+      </c>
+      <c r="M17" s="105">
         <f t="shared" si="4"/>
-        <v>29.300000000000182</v>
-      </c>
-      <c r="N17" s="183">
+        <v>41.5</v>
+      </c>
+      <c r="N17" s="103">
         <f t="shared" si="5"/>
-        <v>36601.890888410009</v>
+        <v>36438.08251421</v>
       </c>
       <c r="O17" s="96">
         <f>N17+'prorrateo '!M10</f>
-        <v>259949.44175612001</v>
+        <v>105443.75104994999</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -4674,42 +4527,42 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="102">
-        <v>2485.1</v>
+        <v>2601.9</v>
       </c>
       <c r="G18" s="102">
-        <v>2601.9</v>
+        <v>2722.4</v>
       </c>
       <c r="H18" s="103">
         <f t="shared" si="1"/>
-        <v>116.80000000000018</v>
+        <v>120.5</v>
       </c>
       <c r="I18" s="104">
         <f t="shared" si="0"/>
-        <v>8.1760000000000144</v>
+        <v>8.4350000000000005</v>
       </c>
       <c r="J18" s="114">
         <f t="shared" si="2"/>
-        <v>10954.321600000017</v>
+        <v>11301.333500000001</v>
       </c>
       <c r="K18" s="114">
         <f>K8*E18%</f>
-        <v>-16247.652377040005</v>
-      </c>
-      <c r="L18" s="219">
+        <v>-17542.813332240003</v>
+      </c>
+      <c r="L18" s="186">
         <f t="shared" si="3"/>
-        <v>33521.378430959994</v>
+        <v>32226.217475760001</v>
       </c>
       <c r="M18" s="105">
         <f t="shared" si="4"/>
-        <v>116.80000000000018</v>
+        <v>120.5</v>
       </c>
       <c r="N18" s="103">
         <f t="shared" si="5"/>
-        <v>44475.700030960012</v>
+        <v>43527.550975760001</v>
       </c>
       <c r="O18" s="96">
         <f>N18+'prorrateo '!M11</f>
-        <v>422724.3683202432</v>
+        <v>225634.09256032002</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4729,42 +4582,42 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="102">
-        <v>4913.8</v>
+        <v>5191</v>
       </c>
       <c r="G19" s="102">
-        <v>5191</v>
+        <v>5568.7</v>
       </c>
       <c r="H19" s="103">
         <f t="shared" si="1"/>
-        <v>277.19999999999982</v>
+        <v>377.69999999999982</v>
       </c>
       <c r="I19" s="104">
         <f t="shared" si="0"/>
-        <v>19.403999999999989</v>
+        <v>26.438999999999989</v>
       </c>
       <c r="J19" s="114">
         <f t="shared" si="2"/>
-        <v>25997.756399999984</v>
+        <v>35423.349899999987</v>
       </c>
       <c r="K19" s="114">
         <f>K8*E19%</f>
-        <v>-16795.688270710005</v>
-      </c>
-      <c r="L19" s="219">
+        <v>-18134.535210510003</v>
+      </c>
+      <c r="L19" s="186">
         <f t="shared" si="3"/>
-        <v>34652.059846289994</v>
+        <v>33313.21290649</v>
       </c>
       <c r="M19" s="105">
         <f>G19-F19</f>
-        <v>277.19999999999982</v>
+        <v>377.69999999999982</v>
       </c>
       <c r="N19" s="103">
         <f t="shared" si="5"/>
-        <v>60649.816246289978</v>
+        <v>68736.562806489994</v>
       </c>
       <c r="O19" s="96">
         <f>N19+'prorrateo '!M12</f>
-        <v>312447.94064428</v>
+        <v>280726.40757167997</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4784,42 +4637,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="102">
-        <v>6379</v>
+        <v>6705</v>
       </c>
       <c r="G20" s="102">
-        <v>6705</v>
+        <v>7045.5</v>
       </c>
       <c r="H20" s="103">
         <f t="shared" si="1"/>
-        <v>326</v>
+        <v>340.5</v>
       </c>
       <c r="I20" s="104">
         <f t="shared" si="0"/>
-        <v>22.820000000000004</v>
+        <v>23.835000000000001</v>
       </c>
       <c r="J20" s="114">
         <f t="shared" si="2"/>
-        <v>30574.562000000002</v>
+        <v>31934.473500000004</v>
       </c>
       <c r="K20" s="114">
         <f>K8*E20%</f>
-        <v>-16473.314215610008</v>
-      </c>
-      <c r="L20" s="219">
+        <v>-17786.463517410004</v>
+      </c>
+      <c r="L20" s="186">
         <f t="shared" si="3"/>
-        <v>33986.953131389993</v>
+        <v>32673.803829590004</v>
       </c>
       <c r="M20" s="105">
         <f t="shared" si="4"/>
-        <v>326</v>
+        <v>340.5</v>
       </c>
       <c r="N20" s="103">
         <f t="shared" si="5"/>
-        <v>64561.515131389999</v>
+        <v>64608.277329590012</v>
       </c>
       <c r="O20" s="96">
         <f>N20+'prorrateo '!M13</f>
-        <v>316602.45902336005</v>
+        <v>269720.25800266967</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -4839,42 +4692,42 @@
         <v>5.09</v>
       </c>
       <c r="F21" s="102">
-        <v>4271.8</v>
+        <v>4338.3</v>
       </c>
       <c r="G21" s="102">
-        <v>4338.3</v>
+        <v>4426.3</v>
       </c>
       <c r="H21" s="103">
         <f t="shared" si="1"/>
-        <v>66.5</v>
+        <v>88</v>
       </c>
       <c r="I21" s="104">
         <f t="shared" si="0"/>
-        <v>4.6550000000000002</v>
+        <v>6.16</v>
       </c>
       <c r="J21" s="114">
         <f t="shared" si="2"/>
-        <v>6236.8355000000001</v>
+        <v>8253.2560000000012</v>
       </c>
       <c r="K21" s="114">
         <f>K8*E21%</f>
-        <v>-16408.839404590006</v>
-      </c>
-      <c r="L21" s="219">
+        <v>-17716.849178790002</v>
+      </c>
+      <c r="L21" s="186">
         <f t="shared" si="3"/>
-        <v>33853.931788409995</v>
+        <v>32545.922014210002</v>
       </c>
       <c r="M21" s="105">
         <f t="shared" si="4"/>
-        <v>66.5</v>
+        <v>88</v>
       </c>
       <c r="N21" s="103">
         <f t="shared" si="5"/>
-        <v>40090.767288409996</v>
+        <v>40799.178014210003</v>
       </c>
       <c r="O21" s="96">
         <f>N21+'prorrateo '!M14</f>
-        <v>266927.27605899284</v>
+        <v>221552.140022507</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -4894,42 +4747,42 @@
         <v>5.04</v>
       </c>
       <c r="F22" s="102">
-        <v>2698.4</v>
+        <v>2797.6</v>
       </c>
       <c r="G22" s="102">
-        <v>2797.6</v>
+        <v>3145.8</v>
       </c>
       <c r="H22" s="103">
         <f t="shared" si="1"/>
-        <v>99.199999999999818</v>
+        <v>348.20000000000027</v>
       </c>
       <c r="I22" s="104">
         <f t="shared" si="0"/>
-        <v>6.9439999999999875</v>
+        <v>24.37400000000002</v>
       </c>
       <c r="J22" s="114">
         <f t="shared" si="2"/>
-        <v>9303.6703999999827</v>
+        <v>32656.633400000028</v>
       </c>
       <c r="K22" s="114">
         <f>K8*E22%</f>
-        <v>-16247.652377040005</v>
-      </c>
-      <c r="L22" s="219">
+        <v>-17542.813332240003</v>
+      </c>
+      <c r="L22" s="186">
         <f t="shared" si="3"/>
-        <v>33521.378430959994</v>
+        <v>32226.217475760001</v>
       </c>
       <c r="M22" s="105">
         <f t="shared" si="4"/>
-        <v>99.199999999999818</v>
+        <v>348.20000000000027</v>
       </c>
       <c r="N22" s="103">
         <f t="shared" si="5"/>
-        <v>42825.048830959975</v>
+        <v>64882.850875760028</v>
       </c>
       <c r="O22" s="96">
         <f>N22+'prorrateo '!M15</f>
-        <v>270561.32804564998</v>
+        <v>506814.6619711176</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -4949,42 +4802,42 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="102">
-        <v>5255.9</v>
+        <v>5576.5</v>
       </c>
       <c r="G23" s="102">
-        <v>5576.5</v>
+        <v>5835.3</v>
       </c>
       <c r="H23" s="103">
         <f t="shared" si="1"/>
-        <v>320.60000000000036</v>
+        <v>258.80000000000018</v>
       </c>
       <c r="I23" s="104">
         <f t="shared" si="0"/>
-        <v>22.442000000000029</v>
+        <v>18.116000000000014</v>
       </c>
       <c r="J23" s="114">
         <f t="shared" si="2"/>
-        <v>30068.112200000036</v>
+        <v>24272.075600000018</v>
       </c>
       <c r="K23" s="114">
         <f>K8*E23%</f>
-        <v>-16795.688270710005</v>
-      </c>
-      <c r="L23" s="219">
+        <v>-18134.535210510003</v>
+      </c>
+      <c r="L23" s="186">
         <f t="shared" si="3"/>
-        <v>34652.059846289994</v>
+        <v>33313.21290649</v>
       </c>
       <c r="M23" s="105">
         <f t="shared" si="4"/>
-        <v>320.60000000000036</v>
+        <v>258.80000000000018</v>
       </c>
       <c r="N23" s="103">
         <f t="shared" si="5"/>
-        <v>64720.172046290027</v>
+        <v>57585.288506490018</v>
       </c>
       <c r="O23" s="96">
         <f>N23+'prorrateo '!M16</f>
-        <v>320588.64609535999</v>
+        <v>258423.86103565362</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -5004,42 +4857,42 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="102">
-        <v>1847.5</v>
+        <v>1982.9</v>
       </c>
       <c r="G24" s="102">
-        <v>1982.9</v>
+        <v>2020.8</v>
       </c>
       <c r="H24" s="103">
         <f t="shared" si="1"/>
-        <v>135.40000000000009</v>
+        <v>37.899999999999864</v>
       </c>
       <c r="I24" s="104">
         <f t="shared" si="0"/>
-        <v>9.4780000000000069</v>
+        <v>2.6529999999999907</v>
       </c>
       <c r="J24" s="114">
         <f t="shared" si="2"/>
-        <v>12698.759800000009</v>
+        <v>3554.5272999999875</v>
       </c>
       <c r="K24" s="114">
         <f>K8*E24%</f>
-        <v>-16247.652377040005</v>
-      </c>
-      <c r="L24" s="219">
+        <v>-17542.813332240003</v>
+      </c>
+      <c r="L24" s="186">
         <f t="shared" si="3"/>
-        <v>33521.378430959994</v>
+        <v>32226.217475760001</v>
       </c>
       <c r="M24" s="105">
         <f t="shared" si="4"/>
-        <v>135.40000000000009</v>
+        <v>37.899999999999864</v>
       </c>
       <c r="N24" s="103">
         <f t="shared" si="5"/>
-        <v>46220.138230960001</v>
+        <v>35780.744775759988</v>
       </c>
       <c r="O24" s="96">
         <f>N24+'prorrateo '!M17</f>
-        <v>142459.62970272001</v>
+        <v>311853.79051847034</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -5059,42 +4912,42 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="102">
-        <v>2029.4</v>
+        <v>2155.8000000000002</v>
       </c>
       <c r="G25" s="102">
-        <v>2155.8000000000002</v>
+        <v>2317.3000000000002</v>
       </c>
       <c r="H25" s="103">
         <f t="shared" si="1"/>
-        <v>126.40000000000009</v>
+        <v>161.5</v>
       </c>
       <c r="I25" s="104">
         <f t="shared" si="0"/>
-        <v>8.8480000000000079</v>
+        <v>11.305000000000001</v>
       </c>
       <c r="J25" s="114">
         <f t="shared" si="2"/>
-        <v>11854.67680000001</v>
+        <v>15146.6005</v>
       </c>
       <c r="K25" s="114">
         <f>K8*E25%</f>
-        <v>-16795.688270710005</v>
-      </c>
-      <c r="L25" s="219">
+        <v>-18134.535210510003</v>
+      </c>
+      <c r="L25" s="186">
         <f t="shared" si="3"/>
-        <v>34652.059846289994</v>
+        <v>33313.21290649</v>
       </c>
       <c r="M25" s="105">
         <f t="shared" si="4"/>
-        <v>126.40000000000009</v>
+        <v>161.5</v>
       </c>
       <c r="N25" s="103">
         <f t="shared" si="5"/>
-        <v>46506.736646290003</v>
+        <v>48459.81340649</v>
       </c>
       <c r="O25" s="96">
         <f>N25+'prorrateo '!M18</f>
-        <v>284161.78144428</v>
+        <v>240172.90877167997</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -5114,84 +4967,84 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="102">
-        <v>9428.9</v>
+        <v>9974.5</v>
       </c>
       <c r="G26" s="102">
-        <v>9974.5</v>
+        <v>10444</v>
       </c>
       <c r="H26" s="103">
         <f t="shared" si="1"/>
-        <v>545.60000000000036</v>
+        <v>469.5</v>
       </c>
       <c r="I26" s="104">
         <f t="shared" si="0"/>
-        <v>38.192000000000029</v>
+        <v>32.865000000000002</v>
       </c>
       <c r="J26" s="114">
         <f t="shared" si="2"/>
-        <v>51170.187200000037</v>
+        <v>44032.996500000001</v>
       </c>
       <c r="K26" s="114">
         <f>K8*E26%</f>
-        <v>-23855.680077400011</v>
-      </c>
-      <c r="L26" s="219">
+        <v>-25757.305289400007</v>
+      </c>
+      <c r="L26" s="186">
         <f t="shared" si="3"/>
-        <v>49217.896902599998</v>
+        <v>47316.271690599999</v>
       </c>
       <c r="M26" s="105">
         <f t="shared" si="4"/>
-        <v>545.60000000000036</v>
+        <v>469.5</v>
       </c>
       <c r="N26" s="103">
         <f>J26+L26</f>
-        <v>100388.08410260003</v>
+        <v>91349.268190600007</v>
       </c>
       <c r="O26" s="96">
         <f>N26+'prorrateo '!M19</f>
-        <v>472272.80550320004</v>
+        <v>386167.68925920001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="97">
+      <c r="A27" s="207">
         <v>19</v>
       </c>
-      <c r="B27" s="89">
+      <c r="B27" s="208">
         <v>19</v>
       </c>
-      <c r="C27" s="187" t="s">
+      <c r="C27" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="188"/>
-      <c r="E27" s="189">
+      <c r="D27" s="209"/>
+      <c r="E27" s="210">
         <v>1.08</v>
       </c>
-      <c r="F27" s="182"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="183">
+      <c r="F27" s="211"/>
+      <c r="G27" s="211"/>
+      <c r="H27" s="136">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="184">
+      <c r="I27" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="221">
+      <c r="J27" s="188"/>
+      <c r="K27" s="188"/>
+      <c r="L27" s="189">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
-      </c>
-      <c r="M27" s="186">
-        <v>0</v>
-      </c>
-      <c r="N27" s="183">
+        <v>6905.6180305199996</v>
+      </c>
+      <c r="M27" s="137">
+        <v>0</v>
+      </c>
+      <c r="N27" s="136">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O27" s="96">
         <f>N27+'prorrateo '!M20</f>
-        <v>53990.138593440002</v>
+        <v>442887.93594134407</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -5199,7 +5052,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="89"/>
-      <c r="C28" s="163" t="s">
+      <c r="C28" s="153" t="s">
         <v>66</v>
       </c>
       <c r="D28" s="101"/>
@@ -5211,26 +5064,26 @@
       <c r="H28" s="103">
         <v>0</v>
       </c>
-      <c r="I28" s="164">
+      <c r="I28" s="154">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="165"/>
+      <c r="J28" s="155"/>
       <c r="K28" s="114"/>
-      <c r="L28" s="219">
+      <c r="L28" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M28" s="105">
         <v>0</v>
       </c>
       <c r="N28" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O28" s="96">
         <f>N28+'prorrateo '!M21</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -5239,36 +5092,36 @@
       <c r="C29" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="143"/>
-      <c r="E29" s="143">
+      <c r="D29" s="101"/>
+      <c r="E29" s="101">
         <v>1.08</v>
       </c>
-      <c r="F29" s="143"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="144"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="103"/>
       <c r="I29" s="154"/>
       <c r="J29" s="155"/>
-      <c r="K29" s="222"/>
-      <c r="L29" s="223">
+      <c r="K29" s="114"/>
+      <c r="L29" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
-      </c>
-      <c r="M29" s="145">
-        <v>0</v>
-      </c>
-      <c r="N29" s="144">
+        <v>6905.6180305199996</v>
+      </c>
+      <c r="M29" s="105">
+        <v>0</v>
+      </c>
+      <c r="N29" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O29" s="96">
         <f>N29+'prorrateo '!M22</f>
-        <v>406229.68973762408</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
       <c r="B30" s="89"/>
-      <c r="C30" s="163" t="s">
+      <c r="C30" s="153" t="s">
         <v>68</v>
       </c>
       <c r="D30" s="101"/>
@@ -5278,29 +5131,29 @@
       <c r="F30" s="101"/>
       <c r="G30" s="101"/>
       <c r="H30" s="103"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="165"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="155"/>
       <c r="K30" s="114"/>
-      <c r="L30" s="219">
+      <c r="L30" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M30" s="105">
         <v>0</v>
       </c>
       <c r="N30" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O30" s="96">
         <f>N30+'prorrateo '!M23</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="97"/>
       <c r="B31" s="89"/>
-      <c r="C31" s="163" t="s">
+      <c r="C31" s="153" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="101" t="s">
@@ -5312,29 +5165,29 @@
       <c r="F31" s="101"/>
       <c r="G31" s="101"/>
       <c r="H31" s="103"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="165"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="155"/>
       <c r="K31" s="114"/>
-      <c r="L31" s="219">
+      <c r="L31" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M31" s="105">
         <v>0</v>
       </c>
       <c r="N31" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O31" s="96">
         <f>N31+'prorrateo '!M24</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="98"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="163" t="s">
+      <c r="B32" s="171"/>
+      <c r="C32" s="153" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="101" t="s">
@@ -5346,23 +5199,23 @@
       <c r="F32" s="101"/>
       <c r="G32" s="101"/>
       <c r="H32" s="103"/>
-      <c r="I32" s="164"/>
-      <c r="J32" s="165"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="155"/>
       <c r="K32" s="114"/>
-      <c r="L32" s="219">
+      <c r="L32" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M32" s="105">
         <v>0</v>
       </c>
       <c r="N32" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O32" s="96">
         <f>N32+'prorrateo '!M25</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5383,20 +5236,20 @@
       <c r="I33" s="109"/>
       <c r="J33" s="128"/>
       <c r="K33" s="115"/>
-      <c r="L33" s="219">
+      <c r="L33" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M33" s="105">
         <v>0</v>
       </c>
       <c r="N33" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O33" s="96">
         <f>N33+'prorrateo '!M26</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
@@ -5417,20 +5270,20 @@
       <c r="I34" s="109"/>
       <c r="J34" s="128"/>
       <c r="K34" s="115"/>
-      <c r="L34" s="219">
+      <c r="L34" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M34" s="105">
         <v>0</v>
       </c>
       <c r="N34" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O34" s="96">
         <f>N34+'prorrateo '!M27</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5438,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="89"/>
-      <c r="C35" s="163" t="s">
+      <c r="C35" s="153" t="s">
         <v>73</v>
       </c>
       <c r="D35" s="101"/>
@@ -5450,26 +5303,26 @@
       <c r="H35" s="103">
         <v>0</v>
       </c>
-      <c r="I35" s="164">
+      <c r="I35" s="154">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="166"/>
+      <c r="J35" s="156"/>
       <c r="K35" s="114"/>
-      <c r="L35" s="219">
+      <c r="L35" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M35" s="105">
         <v>0</v>
       </c>
       <c r="N35" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O35" s="96">
         <f>N35+'prorrateo '!M28</f>
-        <v>53990.138593440002</v>
+        <v>43506.734048639992</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
@@ -5477,7 +5330,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="89"/>
-      <c r="C36" s="163" t="s">
+      <c r="C36" s="153" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="101" t="s">
@@ -5491,26 +5344,26 @@
       <c r="H36" s="103">
         <v>0</v>
       </c>
-      <c r="I36" s="164">
+      <c r="I36" s="154">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="166"/>
+      <c r="J36" s="156"/>
       <c r="K36" s="114"/>
-      <c r="L36" s="219">
+      <c r="L36" s="186">
         <f t="shared" si="3"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="M36" s="105">
         <v>0</v>
       </c>
       <c r="N36" s="103">
         <f t="shared" si="6"/>
-        <v>7183.1525209199999</v>
+        <v>6905.6180305199996</v>
       </c>
       <c r="O36" s="96">
         <f>N36+'prorrateo '!M29</f>
-        <v>53990.138593440002</v>
+        <v>92534.050827100786</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
@@ -5531,8 +5384,8 @@
         <v>0</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="217"/>
-      <c r="L37" s="218">
+      <c r="K37" s="184"/>
+      <c r="L37" s="185">
         <v>0</v>
       </c>
       <c r="M37" s="124">
@@ -5557,17 +5410,17 @@
       <c r="I38" s="110"/>
       <c r="J38" s="115">
         <f>SUM(J10:J37)</f>
-        <v>322374.05510000011</v>
+        <v>348071.69310000003</v>
       </c>
       <c r="K38" s="111"/>
       <c r="L38" s="111">
         <f>SUM(L10:L37)</f>
-        <v>665106.71490000014</v>
+        <v>639409.07690000057</v>
       </c>
       <c r="M38" s="112"/>
       <c r="N38" s="108">
         <f>SUM(N10:N37)</f>
-        <v>987480.77000000025</v>
+        <v>987480.77000000048</v>
       </c>
       <c r="P38" s="44"/>
     </row>
@@ -5584,13 +5437,13 @@
       <c r="H39" s="92"/>
       <c r="I39" s="93">
         <f>SUM(I10:I38)</f>
-        <v>240.61100000000013</v>
+        <v>259.79100000000005</v>
       </c>
       <c r="J39" s="123"/>
       <c r="K39" s="93"/>
       <c r="L39" s="130">
         <f>L38+J38</f>
-        <v>987480.77000000025</v>
+        <v>987480.7700000006</v>
       </c>
       <c r="M39" s="92"/>
       <c r="N39" s="92"/>
@@ -5600,18 +5453,18 @@
       <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="236"/>
-      <c r="D40" s="234"/>
-      <c r="E40" s="234"/>
-      <c r="F40" s="234"/>
-      <c r="G40" s="234"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="234"/>
-      <c r="J40" s="234"/>
-      <c r="K40" s="234"/>
-      <c r="L40" s="234"/>
-      <c r="M40" s="234"/>
-      <c r="N40" s="234"/>
+      <c r="C40" s="200"/>
+      <c r="D40" s="198"/>
+      <c r="E40" s="198"/>
+      <c r="F40" s="198"/>
+      <c r="G40" s="198"/>
+      <c r="H40" s="198"/>
+      <c r="I40" s="198"/>
+      <c r="J40" s="198"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+      <c r="M40" s="198"/>
+      <c r="N40" s="198"/>
       <c r="O40" s="94"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
@@ -5625,20 +5478,20 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="L44" s="146"/>
+      <c r="L44" s="138"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L45" s="95"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E46" s="147"/>
-      <c r="F46" s="147"/>
-      <c r="G46" s="147"/>
-      <c r="H46" s="147"/>
-      <c r="I46" s="147"/>
-      <c r="J46" s="147"/>
-      <c r="K46" s="147"/>
-      <c r="L46" s="148"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="139"/>
+      <c r="H46" s="139"/>
+      <c r="I46" s="139"/>
+      <c r="J46" s="139"/>
+      <c r="K46" s="139"/>
+      <c r="L46" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/2026/ROSALES/Febrero/expensas rosales Febrero.xlsx
+++ b/2026/ROSALES/Febrero/expensas rosales Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ROSALES\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ROSALES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E658E4-DCA7-4FA4-980F-73EDD43082E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF954B37-B5F3-48CF-A17B-C7B499CDD6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,16 +18,21 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="124">
   <si>
     <t>TOTAL</t>
   </si>
@@ -397,6 +402,9 @@
   </si>
   <si>
     <t>No llego factura</t>
+  </si>
+  <si>
+    <t>ULTIMA CUOTA PLAN DE PAGOS 4B</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1030,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1317,49 +1325,11 @@
     </xf>
     <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1377,6 +1347,45 @@
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1505,9 +1514,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1545,9 +1554,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1580,9 +1589,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1615,9 +1641,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1794,17 +1837,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1812,22 +1855,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1838,51 +1881,51 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>102</v>
       </c>
@@ -1893,18 +1936,18 @@
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="213">
+      <c r="C19" s="199">
         <v>358727.59</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
@@ -1915,7 +1958,7 @@
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="204" t="s">
         <v>120</v>
       </c>
@@ -1926,7 +1969,7 @@
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>121</v>
       </c>
@@ -1937,7 +1980,7 @@
       <c r="D22" s="20"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
@@ -1951,7 +1994,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
       <c r="B24" s="41"/>
       <c r="C24" s="23">
@@ -1959,7 +2002,7 @@
         <v>1773608.09</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
@@ -1968,7 +2011,7 @@
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>96</v>
       </c>
@@ -1980,7 +2023,7 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>97</v>
       </c>
@@ -1991,7 +2034,7 @@
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>117</v>
       </c>
@@ -2002,17 +2045,17 @@
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>106</v>
       </c>
       <c r="B29" s="42"/>
-      <c r="C29" s="206" t="s">
+      <c r="C29" s="192" t="s">
         <v>122</v>
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
         <v>91</v>
       </c>
@@ -2022,7 +2065,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="40"/>
       <c r="B31" s="41"/>
       <c r="C31" s="23">
@@ -2031,7 +2074,7 @@
       </c>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
         <v>6</v>
       </c>
@@ -2042,40 +2085,40 @@
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
       <c r="C35" s="173"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="173"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="157" t="s">
         <v>113</v>
       </c>
@@ -2085,11 +2128,11 @@
       </c>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>15</v>
       </c>
@@ -2100,7 +2143,7 @@
       </c>
       <c r="E41" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>7</v>
       </c>
@@ -2110,13 +2153,13 @@
         <v>2249583.1469999999</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="C45" s="141"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="163" t="s">
         <v>98</v>
       </c>
@@ -2127,7 +2170,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="163" t="s">
         <v>116</v>
       </c>
@@ -2139,17 +2182,17 @@
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="163" t="s">
         <v>95</v>
       </c>
       <c r="B48" s="28"/>
       <c r="C48" s="165">
         <f>'prorrateo '!F31</f>
-        <v>4417369.1316235811</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4309983.1316235811</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="163" t="s">
         <v>110</v>
       </c>
@@ -2158,105 +2201,114 @@
         <v>-987480.77</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="163" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="214">
+        <v>107386</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="163" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="163" t="s">
+      <c r="B51" s="28"/>
+      <c r="C51" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="164">
-        <f>SUM(C46:C50)</f>
+      <c r="B52" s="28"/>
+      <c r="C52" s="164">
+        <f>SUM(C46:C51)</f>
         <v>1039280.7042474523</v>
       </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="190"/>
-      <c r="B53" s="190"/>
-      <c r="C53" s="190"/>
-      <c r="F53" s="44"/>
-    </row>
-    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="191"/>
-      <c r="B54" s="191"/>
-      <c r="C54" s="191"/>
-    </row>
-    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="26" t="s">
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="10"/>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="200"/>
+      <c r="B54" s="200"/>
+      <c r="C54" s="200"/>
+      <c r="F54" s="44"/>
+    </row>
+    <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="201"/>
+      <c r="B55" s="201"/>
+      <c r="C55" s="201"/>
+    </row>
+    <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="29"/>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
+      <c r="B56" s="27"/>
+      <c r="C56" s="29"/>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="31">
+      <c r="B57" s="28"/>
+      <c r="C57" s="31">
         <f>-C41</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="31"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="28"/>
       <c r="B58" s="28"/>
-      <c r="C58" s="32"/>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="143"/>
-      <c r="C59" s="144">
-        <f>SUM(C55:C58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="192" t="s">
+      <c r="C58" s="31"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="32"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="143"/>
+      <c r="C60" s="144">
+        <f>SUM(C56:C59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="202" t="s">
         <v>105</v>
       </c>
-      <c r="B60" s="193"/>
-      <c r="C60" s="193"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="193"/>
-      <c r="B61" s="193"/>
-      <c r="C61" s="193"/>
-    </row>
-    <row r="62" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="193"/>
-      <c r="B62" s="193"/>
-      <c r="C62" s="193"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
+      <c r="B61" s="203"/>
+      <c r="C61" s="203"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="203"/>
+      <c r="B62" s="203"/>
+      <c r="C62" s="203"/>
+    </row>
+    <row r="63" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="203"/>
+      <c r="B63" s="203"/>
+      <c r="C63" s="203"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="A60:C62"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="A61:C63"/>
     <mergeCell ref="A21:B21"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
@@ -2276,58 +2328,58 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="194">
+      <c r="B1" s="206">
         <f>N1</f>
         <v>2249583.1469999999</v>
       </c>
-      <c r="C1" s="194"/>
+      <c r="C1" s="206"/>
       <c r="D1" s="135">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="195">
-        <v>0</v>
-      </c>
-      <c r="H1" s="195"/>
-      <c r="I1" s="196" t="s">
+      <c r="G1" s="207">
+        <v>0</v>
+      </c>
+      <c r="H1" s="207"/>
+      <c r="I1" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="194">
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="206">
         <v>500000</v>
       </c>
-      <c r="M1" s="194"/>
+      <c r="M1" s="206"/>
       <c r="N1">
         <v>2249583.1469999999</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2371,7 +2423,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2425,7 +2477,7 @@
         <v>140503.69881170001</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2476,7 +2528,7 @@
         <v>272296.63031663839</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2528,7 +2580,7 @@
         <v>138578.99007500871</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
@@ -2580,7 +2632,7 @@
       </c>
       <c r="P6" s="159"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2634,7 +2686,7 @@
       </c>
       <c r="P7" s="159"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2649,7 +2701,7 @@
         <v>244451.26649070997</v>
       </c>
       <c r="F8" s="175">
-        <f t="shared" ref="F8:F10" si="8">E8</f>
+        <f t="shared" ref="F8" si="8">E8</f>
         <v>244451.26649070997</v>
       </c>
       <c r="G8" s="181">
@@ -2685,7 +2737,7 @@
         <v>139953.7821823</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2737,11 +2789,11 @@
       </c>
       <c r="P9" s="159"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="202" t="s">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="190" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="203"/>
+      <c r="B10" s="191"/>
       <c r="C10" s="63" t="s">
         <v>45</v>
       </c>
@@ -2752,12 +2804,12 @@
         <v>224924.81309071</v>
       </c>
       <c r="F10" s="175">
-        <f>379452.66-F22</f>
-        <v>332311.00925147999</v>
+        <f>379452.66-107386-F22</f>
+        <v>224925.00925147996</v>
       </c>
       <c r="G10" s="182">
         <f t="shared" si="1"/>
-        <v>-107386.19616076999</v>
+        <v>-0.19616076996317133</v>
       </c>
       <c r="H10" s="64"/>
       <c r="I10" s="64">
@@ -2778,14 +2830,14 @@
       </c>
       <c r="M10" s="174">
         <f t="shared" si="6"/>
-        <v>69005.668535739998</v>
+        <v>176391.66853574003</v>
       </c>
       <c r="O10" s="138">
         <f t="shared" si="7"/>
-        <v>32567.586021529998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>139953.58602153003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>94</v>
       </c>
@@ -2836,7 +2888,7 @@
         <v>138578.9906088</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2887,7 +2939,7 @@
         <v>143253.28195869998</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2941,7 +2993,7 @@
         <v>140503.70334348967</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -2994,7 +3046,7 @@
         <v>139953.78399408696</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3044,7 +3096,7 @@
         <v>377048.96021959756</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3098,7 +3150,7 @@
         <v>143253.28402267362</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3146,7 +3198,7 @@
         <v>240292.30096695037</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="167" t="s">
         <v>61</v>
       </c>
@@ -3200,7 +3252,7 @@
       <c r="P18" s="169"/>
       <c r="Q18" s="166"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3251,11 +3303,11 @@
         <v>203469.15287800002</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="203"/>
+      <c r="B20" s="191"/>
       <c r="C20" s="63" t="s">
         <v>65</v>
       </c>
@@ -3298,7 +3350,7 @@
         <v>429076.69988030411</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3349,7 +3401,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="62" t="s">
         <v>118</v>
       </c>
@@ -3399,7 +3451,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3450,7 +3502,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3503,7 +3555,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3556,7 +3608,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3607,7 +3659,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3662,7 +3714,7 @@
         <v>468461.09567764011</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3714,7 +3766,7 @@
         <v>29695.497987599996</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3764,7 +3816,7 @@
         <v>78722.814766060794</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3779,7 +3831,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3792,7 +3844,7 @@
       <c r="E31" s="73"/>
       <c r="F31" s="132">
         <f>SUM(F3:F30)</f>
-        <v>4417369.1316235811</v>
+        <v>4309983.1316235811</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
@@ -3808,16 +3860,16 @@
       <c r="L31" s="132"/>
       <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>4550612.3728449307</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>4657998.3728449317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F34" s="44"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="21"/>
     </row>
   </sheetData>
@@ -3836,45 +3888,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" customWidth="1"/>
     <col min="6" max="6" width="12" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="5.109375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="197" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="209" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="198"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="198"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="199"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="211"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="146"/>
@@ -3892,7 +3944,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="148"/>
@@ -3910,7 +3962,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="148"/>
@@ -3930,7 +3982,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="148"/>
@@ -3948,7 +4000,7 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
       <c r="C6" s="172" t="str">
@@ -3969,7 +4021,7 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
@@ -3992,7 +4044,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4008,16 +4060,16 @@
         <f>C8-J38</f>
         <v>-348071.69310000003</v>
       </c>
-      <c r="L8" s="201">
+      <c r="L8" s="213">
         <f>C7-J38</f>
         <v>639409.07689999999</v>
       </c>
-      <c r="M8" s="201"/>
+      <c r="M8" s="213"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="86" t="s">
         <v>78</v>
       </c>
@@ -4062,7 +4114,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="97">
         <v>1</v>
       </c>
@@ -4118,7 +4170,7 @@
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="98">
         <v>2</v>
       </c>
@@ -4174,7 +4226,7 @@
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="97">
         <v>3</v>
       </c>
@@ -4233,7 +4285,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="97">
         <v>4</v>
       </c>
@@ -4289,7 +4341,7 @@
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="97">
         <v>6</v>
       </c>
@@ -4345,7 +4397,7 @@
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="97">
         <v>7</v>
       </c>
@@ -4400,7 +4452,7 @@
         <v>264544.09901071998</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="97">
         <v>8</v>
       </c>
@@ -4455,7 +4507,7 @@
         <v>231530.18707088006</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="97">
         <v>9</v>
       </c>
@@ -4507,10 +4559,10 @@
       </c>
       <c r="O17" s="96">
         <f>N17+'prorrateo '!M10</f>
-        <v>105443.75104994999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>212829.75104995002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="97">
         <v>10</v>
       </c>
@@ -4565,7 +4617,7 @@
         <v>225634.09256032002</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="97">
         <v>11</v>
       </c>
@@ -4620,7 +4672,7 @@
         <v>280726.40757167997</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="97">
         <v>12</v>
       </c>
@@ -4675,7 +4727,7 @@
         <v>269720.25800266967</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="97">
         <v>13</v>
       </c>
@@ -4730,7 +4782,7 @@
         <v>221552.140022507</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="97">
         <v>14</v>
       </c>
@@ -4785,7 +4837,7 @@
         <v>506814.6619711176</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="97">
         <v>15</v>
       </c>
@@ -4840,7 +4892,7 @@
         <v>258423.86103565362</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="97">
         <v>16</v>
       </c>
@@ -4895,7 +4947,7 @@
         <v>311853.79051847034</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="97">
         <v>17</v>
       </c>
@@ -4950,7 +5002,7 @@
         <v>240172.90877167997</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="97">
         <v>18</v>
       </c>
@@ -5005,27 +5057,27 @@
         <v>386167.68925920001</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="207">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="193">
         <v>19</v>
       </c>
-      <c r="B27" s="208">
+      <c r="B27" s="194">
         <v>19</v>
       </c>
       <c r="C27" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="209"/>
-      <c r="E27" s="210">
+      <c r="D27" s="195"/>
+      <c r="E27" s="196">
         <v>1.08</v>
       </c>
-      <c r="F27" s="211"/>
-      <c r="G27" s="211"/>
+      <c r="F27" s="197"/>
+      <c r="G27" s="197"/>
       <c r="H27" s="136">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="212">
+      <c r="I27" s="198">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5047,7 +5099,7 @@
         <v>442887.93594134407</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="97">
         <v>20</v>
       </c>
@@ -5086,7 +5138,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="97"/>
       <c r="B29" s="89"/>
       <c r="C29" s="153" t="s">
@@ -5118,7 +5170,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="97"/>
       <c r="B30" s="89"/>
       <c r="C30" s="153" t="s">
@@ -5150,7 +5202,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="97"/>
       <c r="B31" s="89"/>
       <c r="C31" s="153" t="s">
@@ -5184,7 +5236,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="98"/>
       <c r="B32" s="171"/>
       <c r="C32" s="153" t="s">
@@ -5218,7 +5270,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="97"/>
       <c r="B33" s="89"/>
       <c r="C33" s="127" t="s">
@@ -5252,7 +5304,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="97"/>
       <c r="B34" s="89"/>
       <c r="C34" s="127" t="s">
@@ -5286,7 +5338,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="97">
         <v>21</v>
       </c>
@@ -5325,7 +5377,7 @@
         <v>43506.734048639992</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="97">
         <v>22</v>
       </c>
@@ -5366,7 +5418,7 @@
         <v>92534.050827100786</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="97">
         <v>23</v>
       </c>
@@ -5396,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="97">
         <v>24</v>
       </c>
@@ -5424,7 +5476,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="90"/>
       <c r="D39" s="91"/>
@@ -5449,41 +5501,41 @@
       <c r="N39" s="92"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="200"/>
-      <c r="D40" s="198"/>
-      <c r="E40" s="198"/>
-      <c r="F40" s="198"/>
-      <c r="G40" s="198"/>
-      <c r="H40" s="198"/>
-      <c r="I40" s="198"/>
-      <c r="J40" s="198"/>
-      <c r="K40" s="198"/>
-      <c r="L40" s="198"/>
-      <c r="M40" s="198"/>
-      <c r="N40" s="198"/>
+      <c r="C40" s="212"/>
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="210"/>
+      <c r="G40" s="210"/>
+      <c r="H40" s="210"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="210"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
+      <c r="M40" s="210"/>
+      <c r="N40" s="210"/>
       <c r="O40" s="94"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
       <c r="L41" s="95"/>
       <c r="N41" s="96"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="138"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="95"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="139"/>
       <c r="F46" s="139"/>
       <c r="G46" s="139"/>
